--- a/docs/ENReT_v1.0.0_validation_results.xlsx
+++ b/docs/ENReT_v1.0.0_validation_results.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Certified values (NIST)</t>
   </si>
   <si>
-    <t xml:space="preserve">Roszman1: typo in the certified values (known); otherwise all ≥ 5.</t>
+    <t xml:space="preserve">All ≥ 5 except the residual sum of squares of Lanczos1 (certified RSS of 1.4·10⁻²⁵, near the rounding limit of double precision).</t>
   </si>
   <si>
     <t xml:space="preserve">NIST: standard errors</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Certified values: NIST Statistical Reference Datasets (files .dat). App: ENReT v1.0.0, model from “Models for Reference Data”, Levenberg-Marquardt, Max Iterations 1024.</t>
   </si>
   <si>
-    <t xml:space="preserve">LRE = −log10(|App − Certified| / |Certified|), capped at 15 (identical values). Blue: input values; black: formulas. Known issues: Roszman1 (typo in the certified values), Lanczos1 (certified RSS near the rounding limit).</t>
+    <t xml:space="preserve">LRE = −log10(|App − Certified| / |Certified|), capped at 15 (identical values). Blue: input values; black: formulas. Known issue: Lanczos1 (certified RSS near the rounding limit of double precision).</t>
   </si>
   <si>
     <t xml:space="preserve">Dataset</t>
@@ -1130,15 +1130,15 @@
       </c>
       <c r="D5" s="7" t="n">
         <f aca="false">MIN(NIST!G6:G291)</f>
-        <v>0.0798931454551986</v>
+        <v>2.68342669638918</v>
       </c>
       <c r="E5" s="6" t="n">
         <f aca="false">COUNTIF(NIST!G6:G291,"&gt;=5")</f>
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F5" s="8" t="n">
         <f aca="false">E5/C5</f>
-        <v>0.986013986013986</v>
+        <v>0.993006993006993</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>11</v>
@@ -9904,14 +9904,14 @@
         <v>44</v>
       </c>
       <c r="E266" s="12" t="n">
-        <v>1.20196866396</v>
+        <v>0.20196866396</v>
       </c>
       <c r="F266" s="12" t="n">
         <v>0.201968663861161</v>
       </c>
       <c r="G266" s="7" t="n">
         <f aca="false">IF(F266="","",IF(F266=E266,15,MIN(15,-LOG10(ABS(F266-E266)/ABS(E266)))))</f>
-        <v>0.0798931454551986</v>
+        <v>9.31035568254928</v>
       </c>
       <c r="H266" s="12" t="n">
         <v>0.019172666023</v>
@@ -10067,14 +10067,14 @@
         <v>44</v>
       </c>
       <c r="E271" s="12" t="n">
-        <v>1.20196866396</v>
+        <v>0.20196866396</v>
       </c>
       <c r="F271" s="12" t="n">
         <v>0.201968663863301</v>
       </c>
       <c r="G271" s="7" t="n">
         <f aca="false">IF(F271="","",IF(F271=E271,15,MIN(15,-LOG10(ABS(F271-E271)/ABS(E271)))))</f>
-        <v>0.079893145456128</v>
+        <v>9.31986208982936</v>
       </c>
       <c r="H271" s="12" t="n">
         <v>0.019172666023</v>
